--- a/таблицаLFSR.xlsx
+++ b/таблицаLFSR.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artemmihlin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/artemmihlin/Documents/Labs/Rider/ImropveCrypto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916D3FD4-F1F3-144C-914B-5F43E9B11EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABD0BC6-0B10-7642-B140-665B77587EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,11 +173,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -185,11 +188,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -199,6 +197,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF62"/>
+  <dimension ref="A1:AE62"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.83203125" customWidth="1"/>
@@ -490,49 +490,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="5"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15"/>
-      <c r="AD1" s="16"/>
-      <c r="AE1" s="7" t="s">
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="10" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="11">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="6">
         <v>28</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="5">
         <v>27</v>
       </c>
       <c r="E2" s="1">
@@ -589,10 +589,10 @@
       <c r="V2" s="1">
         <v>9</v>
       </c>
-      <c r="W2" s="10">
+      <c r="W2" s="1">
         <v>8</v>
       </c>
-      <c r="X2" s="10">
+      <c r="X2" s="1">
         <v>7</v>
       </c>
       <c r="Y2" s="1">
@@ -601,31 +601,31 @@
       <c r="Z2" s="1">
         <v>5</v>
       </c>
-      <c r="AA2" s="12">
+      <c r="AA2" s="15">
         <v>4</v>
       </c>
-      <c r="AB2" s="1">
+      <c r="AB2" s="16">
         <v>3</v>
       </c>
       <c r="AC2" s="1">
         <v>2</v>
       </c>
-      <c r="AD2" s="10">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="8"/>
+      <c r="AD2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="11"/>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="12">
-        <v>1</v>
-      </c>
-      <c r="D3" s="9">
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
         <v>1</v>
       </c>
       <c r="E3" s="1">
@@ -682,10 +682,10 @@
       <c r="V3" s="1">
         <v>1</v>
       </c>
-      <c r="W3" s="10">
-        <v>1</v>
-      </c>
-      <c r="X3" s="10">
+      <c r="W3" s="1">
+        <v>1</v>
+      </c>
+      <c r="X3" s="1">
         <v>1</v>
       </c>
       <c r="Y3" s="1">
@@ -694,16 +694,16 @@
       <c r="Z3" s="1">
         <v>1</v>
       </c>
-      <c r="AA3" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="1">
+      <c r="AA3" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="16">
         <v>1</v>
       </c>
       <c r="AC3" s="1">
         <v>1</v>
       </c>
-      <c r="AD3" s="10">
+      <c r="AD3" s="1">
         <v>1</v>
       </c>
       <c r="AE3" s="2">
@@ -711,14 +711,14 @@
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A4" s="6"/>
+      <c r="A4" s="8"/>
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="12">
-        <v>1</v>
-      </c>
-      <c r="D4" s="9">
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5">
         <v>1</v>
       </c>
       <c r="E4" s="1">
@@ -775,10 +775,10 @@
       <c r="V4" s="1">
         <v>1</v>
       </c>
-      <c r="W4" s="10">
-        <v>1</v>
-      </c>
-      <c r="X4" s="10">
+      <c r="W4" s="1">
+        <v>1</v>
+      </c>
+      <c r="X4" s="1">
         <v>1</v>
       </c>
       <c r="Y4" s="1">
@@ -787,16 +787,16 @@
       <c r="Z4" s="1">
         <v>1</v>
       </c>
-      <c r="AA4" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="1">
+      <c r="AA4" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="16">
         <v>1</v>
       </c>
       <c r="AC4" s="1">
         <v>1</v>
       </c>
-      <c r="AD4" s="10">
+      <c r="AD4" s="1">
         <v>0</v>
       </c>
       <c r="AE4" s="2">
@@ -804,14 +804,14 @@
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A5" s="6"/>
+      <c r="A5" s="8"/>
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="12">
-        <v>1</v>
-      </c>
-      <c r="D5" s="9">
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
         <v>1</v>
       </c>
       <c r="E5" s="1">
@@ -868,10 +868,10 @@
       <c r="V5" s="1">
         <v>1</v>
       </c>
-      <c r="W5" s="10">
-        <v>1</v>
-      </c>
-      <c r="X5" s="10">
+      <c r="W5" s="1">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1">
         <v>1</v>
       </c>
       <c r="Y5" s="1">
@@ -880,16 +880,16 @@
       <c r="Z5" s="1">
         <v>1</v>
       </c>
-      <c r="AA5" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="1">
+      <c r="AA5" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="16">
         <v>1</v>
       </c>
       <c r="AC5" s="1">
         <v>0</v>
       </c>
-      <c r="AD5" s="10">
+      <c r="AD5" s="1">
         <v>0</v>
       </c>
       <c r="AE5" s="2">
@@ -897,14 +897,14 @@
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A6" s="6"/>
+      <c r="A6" s="8"/>
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5">
         <v>1</v>
       </c>
       <c r="E6" s="1">
@@ -961,10 +961,10 @@
       <c r="V6" s="1">
         <v>1</v>
       </c>
-      <c r="W6" s="10">
-        <v>1</v>
-      </c>
-      <c r="X6" s="10">
+      <c r="W6" s="1">
+        <v>1</v>
+      </c>
+      <c r="X6" s="1">
         <v>1</v>
       </c>
       <c r="Y6" s="1">
@@ -973,31 +973,31 @@
       <c r="Z6" s="1">
         <v>1</v>
       </c>
-      <c r="AA6" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="1">
+      <c r="AA6" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="16">
         <v>0</v>
       </c>
       <c r="AC6" s="1">
         <v>0</v>
       </c>
-      <c r="AD6" s="10">
+      <c r="AD6" s="1">
         <v>0</v>
       </c>
       <c r="AE6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A7" s="6"/>
+      <c r="A7" s="8"/>
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
         <v>1</v>
       </c>
       <c r="E7" s="1">
@@ -1054,10 +1054,10 @@
       <c r="V7" s="1">
         <v>1</v>
       </c>
-      <c r="W7" s="10">
-        <v>1</v>
-      </c>
-      <c r="X7" s="10">
+      <c r="W7" s="1">
+        <v>1</v>
+      </c>
+      <c r="X7" s="1">
         <v>1</v>
       </c>
       <c r="Y7" s="1">
@@ -1066,31 +1066,31 @@
       <c r="Z7" s="1">
         <v>1</v>
       </c>
-      <c r="AA7" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="1">
+      <c r="AA7" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="16">
         <v>0</v>
       </c>
       <c r="AC7" s="1">
         <v>0</v>
       </c>
-      <c r="AD7" s="10">
-        <v>0</v>
+      <c r="AD7" s="1">
+        <v>1</v>
       </c>
       <c r="AE7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A8" s="6"/>
+      <c r="A8" s="8"/>
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="9">
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5">
         <v>1</v>
       </c>
       <c r="E8" s="1">
@@ -1147,10 +1147,10 @@
       <c r="V8" s="1">
         <v>1</v>
       </c>
-      <c r="W8" s="10">
-        <v>1</v>
-      </c>
-      <c r="X8" s="10">
+      <c r="W8" s="1">
+        <v>1</v>
+      </c>
+      <c r="X8" s="1">
         <v>1</v>
       </c>
       <c r="Y8" s="1">
@@ -1159,16 +1159,16 @@
       <c r="Z8" s="1">
         <v>0</v>
       </c>
-      <c r="AA8" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="1">
+      <c r="AA8" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="16">
         <v>0</v>
       </c>
       <c r="AC8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD8" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="1">
         <v>1</v>
       </c>
       <c r="AE8" s="2">
@@ -1176,14 +1176,14 @@
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A9" s="6"/>
+      <c r="A9" s="8"/>
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="9">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5">
         <v>1</v>
       </c>
       <c r="E9" s="1">
@@ -1240,10 +1240,10 @@
       <c r="V9" s="1">
         <v>1</v>
       </c>
-      <c r="W9" s="10">
-        <v>1</v>
-      </c>
-      <c r="X9" s="10">
+      <c r="W9" s="1">
+        <v>1</v>
+      </c>
+      <c r="X9" s="1">
         <v>1</v>
       </c>
       <c r="Y9" s="1">
@@ -1252,31 +1252,31 @@
       <c r="Z9" s="1">
         <v>0</v>
       </c>
-      <c r="AA9" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0</v>
+      <c r="AA9" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="16">
+        <v>1</v>
       </c>
       <c r="AC9" s="3">
         <v>1</v>
       </c>
-      <c r="AD9" s="10">
+      <c r="AD9" s="1">
         <v>1</v>
       </c>
       <c r="AE9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A10" s="6"/>
+      <c r="A10" s="8"/>
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5">
         <v>1</v>
       </c>
       <c r="E10" s="1">
@@ -1333,10 +1333,10 @@
       <c r="V10" s="1">
         <v>1</v>
       </c>
-      <c r="W10" s="10">
-        <v>1</v>
-      </c>
-      <c r="X10" s="10">
+      <c r="W10" s="1">
+        <v>1</v>
+      </c>
+      <c r="X10" s="1">
         <v>0</v>
       </c>
       <c r="Y10" s="1">
@@ -1345,31 +1345,31 @@
       <c r="Z10" s="1">
         <v>0</v>
       </c>
-      <c r="AA10" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="1">
+      <c r="AA10" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="16">
         <v>1</v>
       </c>
       <c r="AC10" s="1">
         <v>1</v>
       </c>
-      <c r="AD10" s="10">
-        <v>1</v>
+      <c r="AD10" s="1">
+        <v>0</v>
       </c>
       <c r="AE10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A11" s="6"/>
+      <c r="A11" s="8"/>
       <c r="B11" s="1">
         <v>9</v>
       </c>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="9">
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5">
         <v>1</v>
       </c>
       <c r="E11" s="1">
@@ -1426,43 +1426,43 @@
       <c r="V11" s="1">
         <v>1</v>
       </c>
-      <c r="W11" s="10">
-        <v>0</v>
-      </c>
-      <c r="X11" s="10">
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
         <v>0</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
       </c>
       <c r="Z11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="16">
         <v>1</v>
       </c>
       <c r="AC11" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD11" s="1">
+        <v>0</v>
       </c>
       <c r="AE11" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A12" s="6"/>
+      <c r="A12" s="8"/>
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9">
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5">
         <v>1</v>
       </c>
       <c r="E12" s="1">
@@ -1519,43 +1519,43 @@
       <c r="V12" s="1">
         <v>0</v>
       </c>
-      <c r="W12" s="10">
-        <v>0</v>
-      </c>
-      <c r="X12" s="10">
+      <c r="W12" s="1">
+        <v>0</v>
+      </c>
+      <c r="X12" s="1">
         <v>0</v>
       </c>
       <c r="Y12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="1">
         <v>1</v>
       </c>
-      <c r="AA12" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>1</v>
+      <c r="AA12" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="16">
+        <v>0</v>
       </c>
       <c r="AC12" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="1">
         <v>0</v>
       </c>
       <c r="AE12" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A13" s="6"/>
+      <c r="A13" s="8"/>
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9">
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5">
         <v>1</v>
       </c>
       <c r="E13" s="1">
@@ -1612,11 +1612,11 @@
       <c r="V13" s="1">
         <v>0</v>
       </c>
-      <c r="W13" s="10">
-        <v>0</v>
-      </c>
-      <c r="X13" s="10">
-        <v>0</v>
+      <c r="W13" s="1">
+        <v>0</v>
+      </c>
+      <c r="X13" s="1">
+        <v>1</v>
       </c>
       <c r="Y13" s="1">
         <v>1</v>
@@ -1624,31 +1624,31 @@
       <c r="Z13" s="1">
         <v>1</v>
       </c>
-      <c r="AA13" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="1">
-        <v>1</v>
+      <c r="AA13" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="16">
+        <v>0</v>
       </c>
       <c r="AC13" s="1">
         <v>0</v>
       </c>
-      <c r="AD13" s="10">
-        <v>0</v>
+      <c r="AD13" s="1">
+        <v>1</v>
       </c>
       <c r="AE13" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A14" s="6"/>
+      <c r="A14" s="8"/>
       <c r="B14" s="1">
         <v>12</v>
       </c>
-      <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
+      <c r="C14" s="7">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5">
         <v>1</v>
       </c>
       <c r="E14" s="1">
@@ -1705,43 +1705,43 @@
       <c r="V14" s="1">
         <v>0</v>
       </c>
-      <c r="W14" s="10">
-        <v>0</v>
-      </c>
-      <c r="X14" s="10">
+      <c r="W14" s="1">
+        <v>1</v>
+      </c>
+      <c r="X14" s="1">
         <v>1</v>
       </c>
       <c r="Y14" s="1">
         <v>1</v>
       </c>
       <c r="Z14" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="16">
         <v>0</v>
       </c>
       <c r="AC14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD14" s="1">
+        <v>1</v>
       </c>
       <c r="AE14" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A15" s="6"/>
+      <c r="A15" s="8"/>
       <c r="B15" s="1">
         <v>13</v>
       </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="9">
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5">
         <v>1</v>
       </c>
       <c r="E15" s="1">
@@ -1796,45 +1796,45 @@
         <v>0</v>
       </c>
       <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="10">
-        <v>1</v>
-      </c>
-      <c r="X15" s="10">
+        <v>1</v>
+      </c>
+      <c r="W15" s="1">
+        <v>1</v>
+      </c>
+      <c r="X15" s="1">
         <v>1</v>
       </c>
       <c r="Y15" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="16">
+        <v>1</v>
       </c>
       <c r="AC15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>1</v>
       </c>
       <c r="AE15" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="A16" s="6"/>
+      <c r="A16" s="8"/>
       <c r="B16" s="1">
         <v>14</v>
       </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9">
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="5">
         <v>1</v>
       </c>
       <c r="E16" s="1">
@@ -1886,48 +1886,48 @@
         <v>0</v>
       </c>
       <c r="U16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="1">
         <v>1</v>
       </c>
-      <c r="W16" s="10">
-        <v>1</v>
-      </c>
-      <c r="X16" s="10">
-        <v>1</v>
+      <c r="W16" s="1">
+        <v>1</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
       </c>
       <c r="Y16" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="1">
         <v>0</v>
       </c>
-      <c r="AA16" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="1">
-        <v>0</v>
+      <c r="AA16" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="16">
+        <v>1</v>
       </c>
       <c r="AC16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="10">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AD16" s="1">
+        <v>0</v>
       </c>
       <c r="AE16" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A17" s="6"/>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A17" s="8"/>
       <c r="B17" s="1">
         <v>15</v>
       </c>
-      <c r="C17" s="12">
-        <v>1</v>
-      </c>
-      <c r="D17" s="9">
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5">
         <v>1</v>
       </c>
       <c r="E17" s="1">
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="T17" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" s="1">
         <v>1</v>
@@ -1984,43 +1984,43 @@
       <c r="V17" s="1">
         <v>1</v>
       </c>
-      <c r="W17" s="10">
-        <v>1</v>
-      </c>
-      <c r="X17" s="10">
-        <v>1</v>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
       </c>
       <c r="Y17" s="1">
         <v>0</v>
       </c>
       <c r="Z17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA17" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="16">
+        <v>1</v>
       </c>
       <c r="AC17" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>0</v>
       </c>
       <c r="AE17" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A18" s="6"/>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A18" s="8"/>
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="12">
-        <v>1</v>
-      </c>
-      <c r="D18" s="9">
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="5">
         <v>1</v>
       </c>
       <c r="E18" s="1">
@@ -2066,7 +2066,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" s="1">
         <v>1</v>
@@ -2075,45 +2075,45 @@
         <v>1</v>
       </c>
       <c r="V18" s="1">
-        <v>1</v>
-      </c>
-      <c r="W18" s="10">
-        <v>1</v>
-      </c>
-      <c r="X18" s="10">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
         <v>0</v>
       </c>
       <c r="Y18" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA18" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="16">
+        <v>0</v>
       </c>
       <c r="AC18" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD18" s="1">
+        <v>0</v>
       </c>
       <c r="AE18" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A19" s="6"/>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A19" s="8"/>
       <c r="B19" s="1">
         <v>17</v>
       </c>
-      <c r="C19" s="12">
-        <v>1</v>
-      </c>
-      <c r="D19" s="9">
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5">
         <v>1</v>
       </c>
       <c r="E19" s="1">
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
       <c r="R19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" s="1">
         <v>1</v>
@@ -2165,48 +2165,48 @@
         <v>1</v>
       </c>
       <c r="U19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" s="1">
-        <v>1</v>
-      </c>
-      <c r="W19" s="10">
-        <v>0</v>
-      </c>
-      <c r="X19" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="1">
+        <v>1</v>
       </c>
       <c r="Y19" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA19" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="16">
+        <v>0</v>
       </c>
       <c r="AC19" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="1">
         <v>1</v>
       </c>
       <c r="AE19" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A20" s="8"/>
       <c r="B20" s="1">
         <v>18</v>
       </c>
-      <c r="C20" s="12">
-        <v>1</v>
-      </c>
-      <c r="D20" s="9">
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="5">
         <v>1</v>
       </c>
       <c r="E20" s="1">
@@ -2246,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="Q20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="1">
         <v>1</v>
@@ -2255,51 +2255,51 @@
         <v>1</v>
       </c>
       <c r="T20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
       </c>
-      <c r="W20" s="10">
-        <v>0</v>
-      </c>
-      <c r="X20" s="10">
-        <v>0</v>
+      <c r="W20" s="1">
+        <v>1</v>
+      </c>
+      <c r="X20" s="1">
+        <v>1</v>
       </c>
       <c r="Y20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z20" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA20" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="16">
+        <v>0</v>
       </c>
       <c r="AC20" s="1">
         <v>1</v>
       </c>
-      <c r="AD20" s="10">
-        <v>0</v>
+      <c r="AD20" s="1">
+        <v>1</v>
       </c>
       <c r="AE20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A21" s="6"/>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A21" s="8"/>
       <c r="B21" s="1">
         <v>19</v>
       </c>
-      <c r="C21" s="12">
-        <v>1</v>
-      </c>
-      <c r="D21" s="9">
+      <c r="C21" s="7">
+        <v>1</v>
+      </c>
+      <c r="D21" s="5">
         <v>1</v>
       </c>
       <c r="E21" s="1">
@@ -2336,7 +2336,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="1">
         <v>1</v>
@@ -2345,54 +2345,54 @@
         <v>1</v>
       </c>
       <c r="S21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
       </c>
       <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="10">
-        <v>0</v>
-      </c>
-      <c r="X21" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W21" s="1">
+        <v>1</v>
+      </c>
+      <c r="X21" s="1">
+        <v>1</v>
       </c>
       <c r="Y21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="16">
         <v>1</v>
       </c>
       <c r="AC21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>1</v>
       </c>
       <c r="AE21" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A22" s="6"/>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A22" s="8"/>
       <c r="B22" s="1">
         <v>20</v>
       </c>
-      <c r="C22" s="12">
-        <v>1</v>
-      </c>
-      <c r="D22" s="9">
+      <c r="C22" s="7">
+        <v>1</v>
+      </c>
+      <c r="D22" s="5">
         <v>1</v>
       </c>
       <c r="E22" s="1">
@@ -2426,7 +2426,7 @@
         <v>0</v>
       </c>
       <c r="O22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" s="1">
         <v>1</v>
@@ -2435,57 +2435,57 @@
         <v>1</v>
       </c>
       <c r="R22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" s="1">
         <v>0</v>
       </c>
       <c r="U22" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="10">
-        <v>0</v>
-      </c>
-      <c r="X22" s="10">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="W22" s="1">
+        <v>1</v>
+      </c>
+      <c r="X22" s="1">
+        <v>0</v>
       </c>
       <c r="Y22" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AA22" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="16">
+        <v>1</v>
       </c>
       <c r="AC22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="1">
         <v>0</v>
       </c>
       <c r="AE22" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A23" s="6"/>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A23" s="8"/>
       <c r="B23" s="1">
         <v>21</v>
       </c>
-      <c r="C23" s="12">
-        <v>1</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="7">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5">
         <v>1</v>
       </c>
       <c r="E23" s="1">
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" s="1">
         <v>1</v>
@@ -2525,60 +2525,60 @@
         <v>1</v>
       </c>
       <c r="Q23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23" s="1">
         <v>0</v>
       </c>
       <c r="T23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" s="1">
-        <v>0</v>
-      </c>
-      <c r="W23" s="10">
-        <v>1</v>
-      </c>
-      <c r="X23" s="10">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
       </c>
       <c r="Y23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
         <v>1</v>
       </c>
-      <c r="AA23" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="1">
-        <v>0</v>
+      <c r="AA23" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="16">
+        <v>1</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
       </c>
-      <c r="AD23" s="10">
+      <c r="AD23" s="1">
         <v>0</v>
       </c>
       <c r="AE23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A24" s="6"/>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A24" s="8"/>
       <c r="B24" s="1">
         <v>22</v>
       </c>
-      <c r="C24" s="12">
-        <v>1</v>
-      </c>
-      <c r="D24" s="9">
+      <c r="C24" s="7">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5">
         <v>1</v>
       </c>
       <c r="E24" s="1">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="1">
         <v>1</v>
@@ -2615,63 +2615,63 @@
         <v>1</v>
       </c>
       <c r="P24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" s="1">
         <v>0</v>
       </c>
       <c r="S24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" s="1">
-        <v>1</v>
-      </c>
-      <c r="W24" s="10">
-        <v>1</v>
-      </c>
-      <c r="X24" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
       </c>
       <c r="Y24" s="1">
         <v>1</v>
       </c>
       <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="16">
         <v>0</v>
       </c>
       <c r="AC24" s="1">
         <v>0</v>
       </c>
-      <c r="AD24" s="10">
-        <v>1</v>
+      <c r="AD24" s="1">
+        <v>0</v>
       </c>
       <c r="AE24" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A25" s="8"/>
       <c r="B25" s="1">
         <v>23</v>
       </c>
-      <c r="C25" s="12">
-        <v>1</v>
-      </c>
-      <c r="D25" s="9">
+      <c r="C25" s="7">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5">
         <v>1</v>
       </c>
       <c r="E25" s="1">
@@ -2696,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="L25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" s="1">
         <v>1</v>
@@ -2705,66 +2705,66 @@
         <v>1</v>
       </c>
       <c r="O25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="1">
         <v>0</v>
       </c>
       <c r="R25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="1">
-        <v>1</v>
-      </c>
-      <c r="W25" s="10">
-        <v>1</v>
-      </c>
-      <c r="X25" s="10">
+        <v>0</v>
+      </c>
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
         <v>1</v>
       </c>
       <c r="Y25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="16">
         <v>0</v>
       </c>
       <c r="AC25" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="1">
         <v>1</v>
       </c>
       <c r="AE25" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A26" s="6"/>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A26" s="8"/>
       <c r="B26" s="1">
         <v>24</v>
       </c>
-      <c r="C26" s="12">
-        <v>1</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="C26" s="7">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5">
         <v>1</v>
       </c>
       <c r="E26" s="1">
@@ -2786,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="1">
         <v>1</v>
@@ -2795,69 +2795,69 @@
         <v>1</v>
       </c>
       <c r="N26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P26" s="1">
         <v>0</v>
       </c>
       <c r="Q26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V26" s="1">
-        <v>1</v>
-      </c>
-      <c r="W26" s="10">
-        <v>1</v>
-      </c>
-      <c r="X26" s="10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W26" s="1">
+        <v>1</v>
+      </c>
+      <c r="X26" s="1">
+        <v>1</v>
       </c>
       <c r="Y26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="1">
         <v>0</v>
       </c>
-      <c r="AA26" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="1">
-        <v>1</v>
+      <c r="AA26" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="16">
+        <v>0</v>
       </c>
       <c r="AC26" s="1">
         <v>1</v>
       </c>
-      <c r="AD26" s="10">
+      <c r="AD26" s="1">
         <v>1</v>
       </c>
       <c r="AE26" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A27" s="6"/>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A27" s="8"/>
       <c r="B27" s="1">
         <v>25</v>
       </c>
-      <c r="C27" s="12">
-        <v>1</v>
-      </c>
-      <c r="D27" s="9">
+      <c r="C27" s="7">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5">
         <v>1</v>
       </c>
       <c r="E27" s="1">
@@ -2876,7 +2876,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="1">
         <v>1</v>
@@ -2885,40 +2885,40 @@
         <v>1</v>
       </c>
       <c r="M27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
       </c>
       <c r="P27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U27" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V27" s="1">
         <v>1</v>
       </c>
-      <c r="W27" s="10">
-        <v>0</v>
-      </c>
-      <c r="X27" s="10">
-        <v>0</v>
+      <c r="W27" s="1">
+        <v>1</v>
+      </c>
+      <c r="X27" s="1">
+        <v>1</v>
       </c>
       <c r="Y27" s="1">
         <v>0</v>
@@ -2926,31 +2926,31 @@
       <c r="Z27" s="1">
         <v>0</v>
       </c>
-      <c r="AA27" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="1">
+      <c r="AA27" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="16">
         <v>1</v>
       </c>
       <c r="AC27" s="1">
         <v>1</v>
       </c>
-      <c r="AD27" s="10">
+      <c r="AD27" s="1">
         <v>1</v>
       </c>
       <c r="AE27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A28" s="6"/>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A28" s="8"/>
       <c r="B28" s="1">
         <v>26</v>
       </c>
-      <c r="C28" s="12">
-        <v>1</v>
-      </c>
-      <c r="D28" s="9">
+      <c r="C28" s="7">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5">
         <v>1</v>
       </c>
       <c r="E28" s="1">
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
         <v>1</v>
@@ -2975,75 +2975,75 @@
         <v>1</v>
       </c>
       <c r="L28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1">
         <v>0</v>
       </c>
       <c r="O28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U28" s="1">
         <v>1</v>
       </c>
       <c r="V28" s="1">
-        <v>0</v>
-      </c>
-      <c r="W28" s="10">
-        <v>0</v>
-      </c>
-      <c r="X28" s="10">
+        <v>1</v>
+      </c>
+      <c r="W28" s="1">
+        <v>1</v>
+      </c>
+      <c r="X28" s="1">
         <v>0</v>
       </c>
       <c r="Y28" s="1">
         <v>0</v>
       </c>
       <c r="Z28" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="16">
         <v>1</v>
       </c>
       <c r="AC28" s="1">
         <v>1</v>
       </c>
-      <c r="AD28" s="10">
+      <c r="AD28" s="1">
         <v>0</v>
       </c>
       <c r="AE28" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A29" s="6"/>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A29" s="8"/>
       <c r="B29" s="1">
         <v>27</v>
       </c>
-      <c r="C29" s="12">
-        <v>1</v>
-      </c>
-      <c r="D29" s="9">
+      <c r="C29" s="7">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5">
         <v>1</v>
       </c>
       <c r="E29" s="1">
@@ -3056,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="1">
         <v>1</v>
@@ -3065,79 +3065,78 @@
         <v>1</v>
       </c>
       <c r="K29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" s="1">
         <v>0</v>
       </c>
       <c r="N29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" s="1">
         <v>1</v>
       </c>
       <c r="U29" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" s="1">
-        <v>0</v>
-      </c>
-      <c r="W29" s="10">
-        <v>0</v>
-      </c>
-      <c r="X29" s="10">
+        <v>1</v>
+      </c>
+      <c r="W29" s="1">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
         <v>0</v>
       </c>
       <c r="Y29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="1">
         <v>1</v>
       </c>
-      <c r="AA29" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB29" s="1">
+      <c r="AA29" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="16">
         <v>1</v>
       </c>
       <c r="AC29" s="1">
         <v>0</v>
       </c>
-      <c r="AD29" s="10">
+      <c r="AD29" s="1">
         <v>0</v>
       </c>
       <c r="AE29" s="2">
         <v>0</v>
       </c>
-      <c r="AF29" s="13"/>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A30" s="6"/>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A30" s="8"/>
       <c r="B30" s="1">
         <v>28</v>
       </c>
-      <c r="C30" s="12">
-        <v>1</v>
-      </c>
-      <c r="D30" s="9">
+      <c r="C30" s="7">
+        <v>1</v>
+      </c>
+      <c r="D30" s="5">
         <v>0</v>
       </c>
       <c r="E30" s="1">
@@ -3147,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" s="1">
         <v>1</v>
@@ -3156,49 +3155,49 @@
         <v>1</v>
       </c>
       <c r="J30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="1">
         <v>0</v>
       </c>
       <c r="M30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30" s="1">
         <v>1</v>
       </c>
       <c r="T30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30" s="1">
         <v>0</v>
       </c>
-      <c r="W30" s="10">
-        <v>0</v>
-      </c>
-      <c r="X30" s="10">
-        <v>1</v>
+      <c r="W30" s="1">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1">
+        <v>0</v>
       </c>
       <c r="Y30" s="1">
         <v>1</v>
@@ -3206,39 +3205,38 @@
       <c r="Z30" s="1">
         <v>1</v>
       </c>
-      <c r="AA30" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB30" s="1">
+      <c r="AA30" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="16">
         <v>0</v>
       </c>
       <c r="AC30" s="1">
         <v>0</v>
       </c>
-      <c r="AD30" s="10">
+      <c r="AD30" s="1">
         <v>0</v>
       </c>
       <c r="AE30" s="2">
         <v>0</v>
       </c>
-      <c r="AF30" s="13"/>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A31" s="6"/>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A31" s="8"/>
       <c r="B31" s="1">
         <v>29</v>
       </c>
-      <c r="C31" s="12">
-        <v>0</v>
-      </c>
-      <c r="D31" s="9">
+      <c r="C31" s="7">
+        <v>0</v>
+      </c>
+      <c r="D31" s="5">
         <v>0</v>
       </c>
       <c r="E31" s="1">
         <v>0</v>
       </c>
       <c r="F31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" s="1">
         <v>1</v>
@@ -3247,40 +3245,40 @@
         <v>1</v>
       </c>
       <c r="I31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="1">
         <v>0</v>
       </c>
       <c r="L31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" s="1">
         <v>1</v>
       </c>
       <c r="S31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="1">
         <v>0</v>
@@ -3288,10 +3286,10 @@
       <c r="V31" s="1">
         <v>0</v>
       </c>
-      <c r="W31" s="10">
-        <v>1</v>
-      </c>
-      <c r="X31" s="10">
+      <c r="W31" s="1">
+        <v>0</v>
+      </c>
+      <c r="X31" s="1">
         <v>1</v>
       </c>
       <c r="Y31" s="1">
@@ -3300,36 +3298,35 @@
       <c r="Z31" s="1">
         <v>1</v>
       </c>
-      <c r="AA31" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB31" s="1">
+      <c r="AA31" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="16">
         <v>0</v>
       </c>
       <c r="AC31" s="1">
         <v>0</v>
       </c>
-      <c r="AD31" s="10">
+      <c r="AD31" s="1">
         <v>0</v>
       </c>
       <c r="AE31" s="4">
         <v>0</v>
       </c>
-      <c r="AF31" s="13"/>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A32" s="6"/>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A32" s="8"/>
       <c r="B32" s="1">
         <v>30</v>
       </c>
-      <c r="C32" s="12">
-        <v>0</v>
-      </c>
-      <c r="D32" s="9">
+      <c r="C32" s="7">
+        <v>0</v>
+      </c>
+      <c r="D32" s="5">
         <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -3338,40 +3335,40 @@
         <v>1</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" s="1">
         <v>0</v>
       </c>
       <c r="K32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="1">
         <v>1</v>
       </c>
       <c r="R32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="1">
         <v>0</v>
@@ -3380,12 +3377,12 @@
         <v>0</v>
       </c>
       <c r="V32" s="1">
-        <v>1</v>
-      </c>
-      <c r="W32" s="10">
-        <v>1</v>
-      </c>
-      <c r="X32" s="10">
+        <v>0</v>
+      </c>
+      <c r="W32" s="1">
+        <v>1</v>
+      </c>
+      <c r="X32" s="1">
         <v>1</v>
       </c>
       <c r="Y32" s="1">
@@ -3394,33 +3391,32 @@
       <c r="Z32" s="1">
         <v>0</v>
       </c>
-      <c r="AA32" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="1">
+      <c r="AA32" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="16">
         <v>0</v>
       </c>
       <c r="AC32" s="1">
         <v>0</v>
       </c>
-      <c r="AD32" s="10">
+      <c r="AD32" s="1">
         <v>0</v>
       </c>
       <c r="AE32" s="2">
         <v>0</v>
       </c>
-      <c r="AF32" s="13"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A33" s="6"/>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A33" s="8"/>
       <c r="B33" s="1">
         <v>31</v>
       </c>
-      <c r="C33" s="12">
-        <v>0</v>
-      </c>
-      <c r="D33" s="9">
-        <v>0</v>
+      <c r="C33" s="7">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5">
+        <v>1</v>
       </c>
       <c r="E33" s="1">
         <v>1</v>
@@ -3429,40 +3425,40 @@
         <v>1</v>
       </c>
       <c r="G33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="1">
         <v>1</v>
       </c>
       <c r="Q33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S33" s="1">
         <v>0</v>
@@ -3471,15 +3467,15 @@
         <v>0</v>
       </c>
       <c r="U33" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V33" s="1">
         <v>1</v>
       </c>
-      <c r="W33" s="10">
-        <v>1</v>
-      </c>
-      <c r="X33" s="10">
+      <c r="W33" s="1">
+        <v>1</v>
+      </c>
+      <c r="X33" s="1">
         <v>1</v>
       </c>
       <c r="Y33" s="1">
@@ -3488,72 +3484,71 @@
       <c r="Z33" s="1">
         <v>0</v>
       </c>
-      <c r="AA33" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="1">
+      <c r="AA33" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="16">
         <v>0</v>
       </c>
       <c r="AC33" s="1">
         <v>0</v>
       </c>
-      <c r="AD33" s="10">
+      <c r="AD33" s="1">
         <v>0</v>
       </c>
       <c r="AE33" s="2">
         <v>0</v>
       </c>
-      <c r="AF33" s="13"/>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A34" s="6"/>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A34" s="8"/>
       <c r="B34" s="1">
         <v>32</v>
       </c>
-      <c r="C34" s="12">
-        <v>0</v>
-      </c>
-      <c r="D34" s="9">
+      <c r="C34" s="7">
+        <v>1</v>
+      </c>
+      <c r="D34" s="5">
         <v>1</v>
       </c>
       <c r="E34" s="1">
         <v>1</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="1">
         <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
         <v>1</v>
       </c>
       <c r="P34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" s="1">
         <v>0</v>
@@ -3562,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U34" s="1">
         <v>1</v>
@@ -3570,10 +3565,10 @@
       <c r="V34" s="1">
         <v>1</v>
       </c>
-      <c r="W34" s="10">
-        <v>1</v>
-      </c>
-      <c r="X34" s="10">
+      <c r="W34" s="1">
+        <v>1</v>
+      </c>
+      <c r="X34" s="1">
         <v>0</v>
       </c>
       <c r="Y34" s="1">
@@ -3582,69 +3577,68 @@
       <c r="Z34" s="1">
         <v>0</v>
       </c>
-      <c r="AA34" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="1">
+      <c r="AA34" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="16">
         <v>0</v>
       </c>
       <c r="AC34" s="1">
         <v>0</v>
       </c>
-      <c r="AD34" s="10">
+      <c r="AD34" s="1">
         <v>0</v>
       </c>
       <c r="AE34" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A35" s="6"/>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
       <c r="B35" s="1">
         <v>33</v>
       </c>
-      <c r="C35" s="12">
-        <v>1</v>
-      </c>
-      <c r="D35" s="9">
+      <c r="C35" s="7">
+        <v>1</v>
+      </c>
+      <c r="D35" s="5">
         <v>1</v>
       </c>
       <c r="E35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
       <c r="H35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" s="1">
         <v>1</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="1">
         <v>0</v>
@@ -3653,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35" s="1">
         <v>1</v>
@@ -3664,10 +3658,10 @@
       <c r="V35" s="1">
         <v>1</v>
       </c>
-      <c r="W35" s="10">
-        <v>0</v>
-      </c>
-      <c r="X35" s="10">
+      <c r="W35" s="1">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1">
         <v>0</v>
       </c>
       <c r="Y35" s="1">
@@ -3676,66 +3670,65 @@
       <c r="Z35" s="1">
         <v>0</v>
       </c>
-      <c r="AA35" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="1">
+      <c r="AA35" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="16">
         <v>0</v>
       </c>
       <c r="AC35" s="1">
         <v>0</v>
       </c>
-      <c r="AD35" s="10">
-        <v>0</v>
+      <c r="AD35" s="1">
+        <v>1</v>
       </c>
       <c r="AE35" s="2">
         <v>1</v>
       </c>
-      <c r="AF35" s="13"/>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A36" s="6"/>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A36" s="8"/>
       <c r="B36" s="1">
         <v>34</v>
       </c>
-      <c r="C36" s="12">
-        <v>1</v>
-      </c>
-      <c r="D36" s="9">
-        <v>1</v>
+      <c r="C36" s="7">
+        <v>1</v>
+      </c>
+      <c r="D36" s="5">
+        <v>0</v>
       </c>
       <c r="E36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
       </c>
       <c r="G36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <v>1</v>
       </c>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" s="1">
         <v>0</v>
@@ -3744,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="R36" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36" s="1">
         <v>1</v>
@@ -3758,10 +3751,10 @@
       <c r="V36" s="1">
         <v>0</v>
       </c>
-      <c r="W36" s="10">
-        <v>0</v>
-      </c>
-      <c r="X36" s="10">
+      <c r="W36" s="1">
+        <v>0</v>
+      </c>
+      <c r="X36" s="1">
         <v>0</v>
       </c>
       <c r="Y36" s="1">
@@ -3770,63 +3763,62 @@
       <c r="Z36" s="1">
         <v>0</v>
       </c>
-      <c r="AA36" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
+      <c r="AA36" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="16">
         <v>0</v>
       </c>
       <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD36" s="1">
         <v>1</v>
       </c>
       <c r="AE36" s="2">
         <v>1</v>
       </c>
-      <c r="AF36" s="13"/>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A37" s="6"/>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A37" s="8"/>
       <c r="B37" s="1">
         <v>35</v>
       </c>
-      <c r="C37" s="12">
-        <v>1</v>
-      </c>
-      <c r="D37" s="9">
-        <v>1</v>
+      <c r="C37" s="7">
+        <v>0</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
       </c>
       <c r="E37" s="1">
         <v>0</v>
       </c>
       <c r="F37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="1">
         <v>1</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -3835,7 +3827,7 @@
         <v>0</v>
       </c>
       <c r="Q37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" s="1">
         <v>1</v>
@@ -3852,10 +3844,10 @@
       <c r="V37" s="1">
         <v>0</v>
       </c>
-      <c r="W37" s="10">
-        <v>0</v>
-      </c>
-      <c r="X37" s="10">
+      <c r="W37" s="1">
+        <v>0</v>
+      </c>
+      <c r="X37" s="1">
         <v>0</v>
       </c>
       <c r="Y37" s="1">
@@ -3864,60 +3856,59 @@
       <c r="Z37" s="1">
         <v>0</v>
       </c>
-      <c r="AA37" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB37" s="1">
-        <v>0</v>
+      <c r="AA37" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="16">
+        <v>1</v>
       </c>
       <c r="AC37" s="1">
         <v>1</v>
       </c>
-      <c r="AD37" s="10">
+      <c r="AD37" s="1">
         <v>1</v>
       </c>
       <c r="AE37" s="2">
         <v>1</v>
       </c>
-      <c r="AF37" s="13"/>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A38" s="6"/>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A38" s="8"/>
       <c r="B38" s="1">
         <v>36</v>
       </c>
-      <c r="C38" s="12">
-        <v>1</v>
-      </c>
-      <c r="D38" s="9">
+      <c r="C38" s="7">
+        <v>0</v>
+      </c>
+      <c r="D38" s="5">
         <v>0</v>
       </c>
       <c r="E38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" s="1">
         <v>1</v>
       </c>
       <c r="L38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" s="1">
         <v>0</v>
@@ -3926,7 +3917,7 @@
         <v>0</v>
       </c>
       <c r="P38" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" s="1">
         <v>1</v>
@@ -3946,10 +3937,10 @@
       <c r="V38" s="1">
         <v>0</v>
       </c>
-      <c r="W38" s="10">
-        <v>0</v>
-      </c>
-      <c r="X38" s="10">
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
         <v>0</v>
       </c>
       <c r="Y38" s="1">
@@ -3958,57 +3949,56 @@
       <c r="Z38" s="1">
         <v>0</v>
       </c>
-      <c r="AA38" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="1">
+      <c r="AA38" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="16">
         <v>1</v>
       </c>
       <c r="AC38" s="1">
         <v>1</v>
       </c>
-      <c r="AD38" s="10">
+      <c r="AD38" s="1">
         <v>1</v>
       </c>
       <c r="AE38" s="2">
         <v>1</v>
       </c>
-      <c r="AF38" s="13"/>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A39" s="6"/>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A39" s="8"/>
       <c r="B39" s="1">
         <v>37</v>
       </c>
-      <c r="C39" s="12">
-        <v>0</v>
-      </c>
-      <c r="D39" s="9">
-        <v>0</v>
+      <c r="C39" s="7">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5">
+        <v>1</v>
       </c>
       <c r="E39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="1">
         <v>1</v>
       </c>
       <c r="K39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -4017,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="O39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39" s="1">
         <v>1</v>
@@ -4040,66 +4030,65 @@
       <c r="V39" s="1">
         <v>0</v>
       </c>
-      <c r="W39" s="10">
-        <v>0</v>
-      </c>
-      <c r="X39" s="10">
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
         <v>0</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
       </c>
       <c r="Z39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB39" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="16">
         <v>1</v>
       </c>
       <c r="AC39" s="1">
         <v>1</v>
       </c>
-      <c r="AD39" s="10">
+      <c r="AD39" s="1">
         <v>1</v>
       </c>
       <c r="AE39" s="2">
         <v>1</v>
       </c>
-      <c r="AF39" s="13"/>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A40" s="6"/>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A40" s="8"/>
       <c r="B40" s="1">
         <v>38</v>
       </c>
-      <c r="C40" s="12">
-        <v>0</v>
-      </c>
-      <c r="D40" s="9">
-        <v>0</v>
+      <c r="C40" s="7">
+        <v>1</v>
+      </c>
+      <c r="D40" s="5">
+        <v>1</v>
       </c>
       <c r="E40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="J40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
@@ -4108,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="N40" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
         <v>1</v>
@@ -4134,63 +4123,62 @@
       <c r="V40" s="1">
         <v>0</v>
       </c>
-      <c r="W40" s="10">
-        <v>0</v>
-      </c>
-      <c r="X40" s="10">
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
         <v>0</v>
       </c>
       <c r="Y40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="1">
         <v>1</v>
       </c>
-      <c r="AA40" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="1">
+      <c r="AA40" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="16">
         <v>1</v>
       </c>
       <c r="AC40" s="1">
         <v>1</v>
       </c>
-      <c r="AD40" s="10">
+      <c r="AD40" s="1">
         <v>1</v>
       </c>
       <c r="AE40" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A41" s="6"/>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A41" s="8"/>
       <c r="B41" s="1">
         <v>39</v>
       </c>
-      <c r="C41" s="12">
-        <v>0</v>
-      </c>
-      <c r="D41" s="9">
-        <v>0</v>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1</v>
       </c>
       <c r="E41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
         <v>1</v>
       </c>
       <c r="I41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" s="1">
         <v>0</v>
@@ -4199,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" s="1">
         <v>1</v>
@@ -4228,11 +4216,11 @@
       <c r="V41" s="1">
         <v>0</v>
       </c>
-      <c r="W41" s="10">
-        <v>0</v>
-      </c>
-      <c r="X41" s="10">
-        <v>0</v>
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
+        <v>1</v>
       </c>
       <c r="Y41" s="1">
         <v>1</v>
@@ -4240,48 +4228,47 @@
       <c r="Z41" s="1">
         <v>1</v>
       </c>
-      <c r="AA41" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="1">
+      <c r="AA41" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="16">
         <v>1</v>
       </c>
       <c r="AC41" s="1">
         <v>1</v>
       </c>
-      <c r="AD41" s="10">
-        <v>1</v>
+      <c r="AD41" s="1">
+        <v>0</v>
       </c>
       <c r="AE41" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A42" s="6"/>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A42" s="8"/>
       <c r="B42" s="1">
         <v>40</v>
       </c>
-      <c r="C42" s="12">
-        <v>0</v>
-      </c>
-      <c r="D42" s="9">
-        <v>1</v>
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="5">
+        <v>0</v>
       </c>
       <c r="E42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
       </c>
       <c r="H42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="1">
         <v>0</v>
@@ -4290,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="L42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" s="1">
         <v>1</v>
@@ -4322,10 +4309,10 @@
       <c r="V42" s="1">
         <v>0</v>
       </c>
-      <c r="W42" s="10">
-        <v>0</v>
-      </c>
-      <c r="X42" s="10">
+      <c r="W42" s="1">
+        <v>1</v>
+      </c>
+      <c r="X42" s="1">
         <v>1</v>
       </c>
       <c r="Y42" s="1">
@@ -4334,45 +4321,44 @@
       <c r="Z42" s="1">
         <v>1</v>
       </c>
-      <c r="AA42" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="1">
+      <c r="AA42" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="16">
         <v>1</v>
       </c>
       <c r="AC42" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD42" s="1">
+        <v>0</v>
       </c>
       <c r="AE42" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A43" s="6"/>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A43" s="8"/>
       <c r="B43" s="1">
         <v>41</v>
       </c>
-      <c r="C43" s="12">
-        <v>1</v>
-      </c>
-      <c r="D43" s="9">
-        <v>1</v>
+      <c r="C43" s="7">
+        <v>0</v>
+      </c>
+      <c r="D43" s="5">
+        <v>0</v>
       </c>
       <c r="E43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
       </c>
       <c r="G43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" s="1">
         <v>0</v>
@@ -4381,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="K43" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="1">
         <v>1</v>
@@ -4414,12 +4400,12 @@
         <v>0</v>
       </c>
       <c r="V43" s="1">
-        <v>0</v>
-      </c>
-      <c r="W43" s="10">
-        <v>1</v>
-      </c>
-      <c r="X43" s="10">
+        <v>1</v>
+      </c>
+      <c r="W43" s="1">
+        <v>1</v>
+      </c>
+      <c r="X43" s="1">
         <v>1</v>
       </c>
       <c r="Y43" s="1">
@@ -4428,42 +4414,41 @@
       <c r="Z43" s="1">
         <v>1</v>
       </c>
-      <c r="AA43" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB43" s="1">
-        <v>1</v>
+      <c r="AA43" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB43" s="16">
+        <v>0</v>
       </c>
       <c r="AC43" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD43" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD43" s="1">
+        <v>0</v>
       </c>
       <c r="AE43" s="2">
         <v>0</v>
       </c>
-      <c r="AF43" s="13"/>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A44" s="6"/>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A44" s="8"/>
       <c r="B44" s="1">
         <v>42</v>
       </c>
-      <c r="C44" s="12">
-        <v>1</v>
-      </c>
-      <c r="D44" s="9">
-        <v>1</v>
+      <c r="C44" s="7">
+        <v>0</v>
+      </c>
+      <c r="D44" s="5">
+        <v>0</v>
       </c>
       <c r="E44" s="1">
         <v>1</v>
       </c>
       <c r="F44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4472,7 +4457,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" s="1">
         <v>1</v>
@@ -4505,15 +4490,15 @@
         <v>0</v>
       </c>
       <c r="U44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="1">
         <v>1</v>
       </c>
-      <c r="W44" s="10">
-        <v>1</v>
-      </c>
-      <c r="X44" s="10">
+      <c r="W44" s="1">
+        <v>1</v>
+      </c>
+      <c r="X44" s="1">
         <v>1</v>
       </c>
       <c r="Y44" s="1">
@@ -4522,39 +4507,38 @@
       <c r="Z44" s="1">
         <v>1</v>
       </c>
-      <c r="AA44" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>1</v>
+      <c r="AA44" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="16">
+        <v>0</v>
       </c>
       <c r="AC44" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD44" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="1">
         <v>0</v>
       </c>
       <c r="AE44" s="2">
         <v>0</v>
       </c>
-      <c r="AF44" s="13"/>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A45" s="6"/>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A45" s="8"/>
       <c r="B45" s="1">
         <v>43</v>
       </c>
-      <c r="C45" s="12">
-        <v>1</v>
-      </c>
-      <c r="D45" s="9">
+      <c r="C45" s="7">
+        <v>0</v>
+      </c>
+      <c r="D45" s="5">
         <v>1</v>
       </c>
       <c r="E45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" s="1">
         <v>0</v>
@@ -4563,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" s="1">
         <v>1</v>
@@ -4596,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U45" s="1">
         <v>1</v>
@@ -4604,48 +4588,47 @@
       <c r="V45" s="1">
         <v>1</v>
       </c>
-      <c r="W45" s="10">
-        <v>1</v>
-      </c>
-      <c r="X45" s="10">
+      <c r="W45" s="1">
+        <v>1</v>
+      </c>
+      <c r="X45" s="1">
         <v>1</v>
       </c>
       <c r="Y45" s="1">
         <v>1</v>
       </c>
       <c r="Z45" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA45" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB45" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="16">
+        <v>0</v>
       </c>
       <c r="AC45" s="1">
         <v>0</v>
       </c>
-      <c r="AD45" s="10">
+      <c r="AD45" s="1">
         <v>0</v>
       </c>
       <c r="AE45" s="2">
         <v>0</v>
       </c>
-      <c r="AF45" s="13"/>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A46" s="6"/>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
       <c r="B46" s="1">
         <v>44</v>
       </c>
-      <c r="C46" s="12">
-        <v>1</v>
-      </c>
-      <c r="D46" s="9">
-        <v>0</v>
+      <c r="C46" s="7">
+        <v>1</v>
+      </c>
+      <c r="D46" s="5">
+        <v>1</v>
       </c>
       <c r="E46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -4654,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="1">
         <v>1</v>
@@ -4687,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="S46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="1">
         <v>1</v>
@@ -4698,45 +4681,44 @@
       <c r="V46" s="1">
         <v>1</v>
       </c>
-      <c r="W46" s="10">
-        <v>1</v>
-      </c>
-      <c r="X46" s="10">
+      <c r="W46" s="1">
+        <v>1</v>
+      </c>
+      <c r="X46" s="1">
         <v>1</v>
       </c>
       <c r="Y46" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA46" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="16">
         <v>0</v>
       </c>
       <c r="AC46" s="1">
         <v>0</v>
       </c>
-      <c r="AD46" s="10">
+      <c r="AD46" s="1">
         <v>0</v>
       </c>
       <c r="AE46" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A47" s="6"/>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A47" s="8"/>
       <c r="B47" s="1">
         <v>45</v>
       </c>
-      <c r="C47" s="12">
-        <v>0</v>
-      </c>
-      <c r="D47" s="9">
-        <v>0</v>
+      <c r="C47" s="7">
+        <v>1</v>
+      </c>
+      <c r="D47" s="5">
+        <v>1</v>
       </c>
       <c r="E47" s="1">
         <v>0</v>
@@ -4745,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
         <v>1</v>
@@ -4778,7 +4760,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" s="1">
         <v>1</v>
@@ -4792,51 +4774,50 @@
       <c r="V47" s="1">
         <v>1</v>
       </c>
-      <c r="W47" s="10">
-        <v>1</v>
-      </c>
-      <c r="X47" s="10">
-        <v>1</v>
+      <c r="W47" s="1">
+        <v>1</v>
+      </c>
+      <c r="X47" s="1">
+        <v>0</v>
       </c>
       <c r="Y47" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA47" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="16">
         <v>0</v>
       </c>
       <c r="AC47" s="1">
         <v>0</v>
       </c>
-      <c r="AD47" s="10">
-        <v>0</v>
+      <c r="AD47" s="1">
+        <v>1</v>
       </c>
       <c r="AE47" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A48" s="6"/>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A48" s="8"/>
       <c r="B48" s="1">
         <v>46</v>
       </c>
-      <c r="C48" s="12">
-        <v>0</v>
-      </c>
-      <c r="D48" s="9">
+      <c r="C48" s="7">
+        <v>1</v>
+      </c>
+      <c r="D48" s="5">
         <v>0</v>
       </c>
       <c r="E48" s="1">
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
         <v>1</v>
@@ -4869,7 +4850,7 @@
         <v>0</v>
       </c>
       <c r="Q48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="1">
         <v>1</v>
@@ -4886,48 +4867,47 @@
       <c r="V48" s="1">
         <v>1</v>
       </c>
-      <c r="W48" s="10">
-        <v>1</v>
-      </c>
-      <c r="X48" s="10">
-        <v>1</v>
+      <c r="W48" s="1">
+        <v>0</v>
+      </c>
+      <c r="X48" s="1">
+        <v>0</v>
       </c>
       <c r="Y48" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="1">
         <v>0</v>
       </c>
-      <c r="AA48" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB48" s="1">
+      <c r="AA48" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="16">
         <v>0</v>
       </c>
       <c r="AC48" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>1</v>
       </c>
       <c r="AE48" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A49" s="6"/>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A49" s="8"/>
       <c r="B49" s="1">
         <v>47</v>
       </c>
-      <c r="C49" s="12">
-        <v>0</v>
-      </c>
-      <c r="D49" s="9">
+      <c r="C49" s="7">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5">
         <v>0</v>
       </c>
       <c r="E49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1">
         <v>1</v>
@@ -4960,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="1">
         <v>1</v>
@@ -4978,13 +4958,13 @@
         <v>1</v>
       </c>
       <c r="V49" s="1">
-        <v>1</v>
-      </c>
-      <c r="W49" s="10">
-        <v>1</v>
-      </c>
-      <c r="X49" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W49" s="1">
+        <v>0</v>
+      </c>
+      <c r="X49" s="1">
+        <v>0</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -4992,33 +4972,32 @@
       <c r="Z49" s="1">
         <v>0</v>
       </c>
-      <c r="AA49" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="1">
-        <v>0</v>
+      <c r="AA49" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="16">
+        <v>1</v>
       </c>
       <c r="AC49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD49" s="1">
+        <v>1</v>
       </c>
       <c r="AE49" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A50" s="6"/>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A50" s="8"/>
       <c r="B50" s="1">
         <v>48</v>
       </c>
-      <c r="C50" s="12">
-        <v>0</v>
-      </c>
-      <c r="D50" s="9">
-        <v>1</v>
+      <c r="C50" s="7">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0</v>
       </c>
       <c r="E50" s="1">
         <v>1</v>
@@ -5051,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50" s="1">
         <v>1</v>
@@ -5069,15 +5048,15 @@
         <v>1</v>
       </c>
       <c r="U50" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="1">
-        <v>1</v>
-      </c>
-      <c r="W50" s="10">
-        <v>1</v>
-      </c>
-      <c r="X50" s="10">
+        <v>0</v>
+      </c>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
         <v>0</v>
       </c>
       <c r="Y50" s="1">
@@ -5086,32 +5065,31 @@
       <c r="Z50" s="1">
         <v>0</v>
       </c>
-      <c r="AA50" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB50" s="1">
-        <v>0</v>
+      <c r="AA50" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="16">
+        <v>1</v>
       </c>
       <c r="AC50" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>1</v>
       </c>
       <c r="AE50" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="13"/>
+        <v>1</v>
+      </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A51" s="6"/>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A51" s="8"/>
       <c r="B51" s="1">
         <v>49</v>
       </c>
-      <c r="C51" s="12">
-        <v>1</v>
-      </c>
-      <c r="D51" s="9">
+      <c r="C51" s="7">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5">
         <v>1</v>
       </c>
       <c r="E51" s="1">
@@ -5142,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="N51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" s="1">
         <v>1</v>
@@ -5160,52 +5138,51 @@
         <v>1</v>
       </c>
       <c r="T51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="1">
-        <v>1</v>
-      </c>
-      <c r="W51" s="10">
-        <v>0</v>
-      </c>
-      <c r="X51" s="10">
+        <v>0</v>
+      </c>
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1">
         <v>0</v>
       </c>
       <c r="Y51" s="1">
         <v>0</v>
       </c>
       <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA51" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB51" s="16">
+        <v>1</v>
       </c>
       <c r="AC51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AD51" s="1">
+        <v>1</v>
       </c>
       <c r="AE51" s="2">
         <v>1</v>
       </c>
-      <c r="AF51" s="13"/>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A52" s="6"/>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A52" s="8"/>
       <c r="B52" s="1">
         <v>50</v>
       </c>
-      <c r="C52" s="12">
-        <v>1</v>
-      </c>
-      <c r="D52" s="9">
+      <c r="C52" s="7">
+        <v>1</v>
+      </c>
+      <c r="D52" s="5">
         <v>1</v>
       </c>
       <c r="E52" s="1">
@@ -5233,7 +5210,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="1">
         <v>1</v>
@@ -5251,55 +5228,54 @@
         <v>1</v>
       </c>
       <c r="S52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V52" s="1">
         <v>0</v>
       </c>
-      <c r="W52" s="10">
-        <v>0</v>
-      </c>
-      <c r="X52" s="10">
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
         <v>0</v>
       </c>
       <c r="Y52" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA52" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="16">
+        <v>1</v>
       </c>
       <c r="AC52" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD52" s="1">
         <v>1</v>
       </c>
       <c r="AE52" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF52" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A53" s="6"/>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A53" s="8"/>
       <c r="B53" s="1">
         <v>51</v>
       </c>
-      <c r="C53" s="12">
-        <v>1</v>
-      </c>
-      <c r="D53" s="9">
+      <c r="C53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="5">
         <v>1</v>
       </c>
       <c r="E53" s="1">
@@ -5324,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="1">
         <v>1</v>
@@ -5342,13 +5318,13 @@
         <v>1</v>
       </c>
       <c r="R53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" s="1">
         <v>0</v>
@@ -5356,44 +5332,43 @@
       <c r="V53" s="1">
         <v>0</v>
       </c>
-      <c r="W53" s="10">
-        <v>0</v>
-      </c>
-      <c r="X53" s="10">
-        <v>0</v>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
+        <v>1</v>
       </c>
       <c r="Y53" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z53" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AA53" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB53" s="16">
+        <v>1</v>
       </c>
       <c r="AC53" s="1">
         <v>1</v>
       </c>
-      <c r="AD53" s="10">
-        <v>1</v>
+      <c r="AD53" s="1">
+        <v>0</v>
       </c>
       <c r="AE53" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF53" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A54" s="6"/>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A54" s="8"/>
       <c r="B54" s="1">
         <v>52</v>
       </c>
-      <c r="C54" s="12">
-        <v>1</v>
-      </c>
-      <c r="D54" s="9">
+      <c r="C54" s="7">
+        <v>1</v>
+      </c>
+      <c r="D54" s="5">
         <v>0</v>
       </c>
       <c r="E54" s="1">
@@ -5415,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="1">
         <v>1</v>
@@ -5433,13 +5408,13 @@
         <v>1</v>
       </c>
       <c r="Q54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" s="1">
         <v>0</v>
@@ -5450,44 +5425,43 @@
       <c r="V54" s="1">
         <v>0</v>
       </c>
-      <c r="W54" s="10">
-        <v>0</v>
-      </c>
-      <c r="X54" s="10">
-        <v>0</v>
+      <c r="W54" s="1">
+        <v>1</v>
+      </c>
+      <c r="X54" s="1">
+        <v>1</v>
       </c>
       <c r="Y54" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z54" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB54" s="1">
+        <v>1</v>
+      </c>
+      <c r="AA54" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="16">
         <v>1</v>
       </c>
       <c r="AC54" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD54" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD54" s="1">
+        <v>0</v>
       </c>
       <c r="AE54" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF54" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="55" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A55" s="6"/>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A55" s="8"/>
       <c r="B55" s="1">
         <v>53</v>
       </c>
-      <c r="C55" s="12">
-        <v>0</v>
-      </c>
-      <c r="D55" s="9">
+      <c r="C55" s="7">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5">
         <v>0</v>
       </c>
       <c r="E55" s="1">
@@ -5506,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K55" s="1">
         <v>1</v>
@@ -5524,13 +5498,13 @@
         <v>1</v>
       </c>
       <c r="P55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55" s="1">
         <v>0</v>
@@ -5542,46 +5516,45 @@
         <v>0</v>
       </c>
       <c r="V55" s="1">
-        <v>0</v>
-      </c>
-      <c r="W55" s="10">
-        <v>0</v>
-      </c>
-      <c r="X55" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W55" s="1">
+        <v>1</v>
+      </c>
+      <c r="X55" s="1">
+        <v>1</v>
       </c>
       <c r="Y55" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z55" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA55" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="AA55" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="16">
+        <v>0</v>
       </c>
       <c r="AC55" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD55" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD55" s="1">
+        <v>0</v>
       </c>
       <c r="AE55" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="56" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A56" s="6"/>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A56" s="8"/>
       <c r="B56" s="1">
         <v>54</v>
       </c>
-      <c r="C56" s="12">
-        <v>0</v>
-      </c>
-      <c r="D56" s="9">
+      <c r="C56" s="7">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5">
         <v>0</v>
       </c>
       <c r="E56" s="1">
@@ -5597,7 +5570,7 @@
         <v>0</v>
       </c>
       <c r="I56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="1">
         <v>1</v>
@@ -5615,13 +5588,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="1">
         <v>0</v>
@@ -5633,49 +5606,48 @@
         <v>0</v>
       </c>
       <c r="U56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="1">
-        <v>0</v>
-      </c>
-      <c r="W56" s="10">
-        <v>0</v>
-      </c>
-      <c r="X56" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W56" s="1">
+        <v>1</v>
+      </c>
+      <c r="X56" s="1">
+        <v>1</v>
       </c>
       <c r="Y56" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z56" s="1">
         <v>1</v>
       </c>
-      <c r="AA56" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB56" s="1">
-        <v>1</v>
+      <c r="AA56" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB56" s="16">
+        <v>0</v>
       </c>
       <c r="AC56" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD56" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD56" s="1">
+        <v>0</v>
       </c>
       <c r="AE56" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="13"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A57" s="6"/>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A57" s="8"/>
       <c r="B57" s="1">
         <v>55</v>
       </c>
-      <c r="C57" s="12">
-        <v>0</v>
-      </c>
-      <c r="D57" s="9">
+      <c r="C57" s="7">
+        <v>0</v>
+      </c>
+      <c r="D57" s="5">
         <v>0</v>
       </c>
       <c r="E57" s="1">
@@ -5688,7 +5660,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57" s="1">
         <v>1</v>
@@ -5706,13 +5678,13 @@
         <v>1</v>
       </c>
       <c r="N57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="1">
         <v>0</v>
@@ -5724,51 +5696,51 @@
         <v>0</v>
       </c>
       <c r="T57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="1">
-        <v>0</v>
-      </c>
-      <c r="W57" s="10">
-        <v>0</v>
-      </c>
-      <c r="X57" s="10">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="W57" s="1">
+        <v>1</v>
+      </c>
+      <c r="X57" s="1">
+        <v>1</v>
       </c>
       <c r="Y57" s="1">
         <v>1</v>
       </c>
       <c r="Z57" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA57" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB57" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA57" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="16">
+        <v>0</v>
       </c>
       <c r="AC57" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD57" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD57" s="1">
+        <v>0</v>
       </c>
       <c r="AE57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A58" s="6"/>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A58" s="8"/>
       <c r="B58" s="1">
         <v>56</v>
       </c>
-      <c r="C58" s="12">
-        <v>0</v>
-      </c>
-      <c r="D58" s="9">
+      <c r="C58" s="7">
+        <v>0</v>
+      </c>
+      <c r="D58" s="5">
         <v>0</v>
       </c>
       <c r="E58" s="1">
@@ -5778,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" s="1">
         <v>1</v>
@@ -5796,13 +5768,13 @@
         <v>1</v>
       </c>
       <c r="M58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1">
         <v>0</v>
@@ -5814,61 +5786,61 @@
         <v>0</v>
       </c>
       <c r="S58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="1">
-        <v>0</v>
-      </c>
-      <c r="W58" s="10">
-        <v>0</v>
-      </c>
-      <c r="X58" s="10">
+        <v>1</v>
+      </c>
+      <c r="W58" s="1">
+        <v>1</v>
+      </c>
+      <c r="X58" s="1">
         <v>1</v>
       </c>
       <c r="Y58" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA58" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB58" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA58" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="16">
+        <v>0</v>
       </c>
       <c r="AC58" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD58" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD58" s="1">
+        <v>0</v>
       </c>
       <c r="AE58" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A59" s="6"/>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A59" s="8"/>
       <c r="B59" s="1">
         <v>57</v>
       </c>
-      <c r="C59" s="12">
-        <v>0</v>
-      </c>
-      <c r="D59" s="9">
+      <c r="C59" s="7">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5">
         <v>0</v>
       </c>
       <c r="E59" s="1">
         <v>0</v>
       </c>
       <c r="F59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" s="1">
         <v>1</v>
@@ -5886,13 +5858,13 @@
         <v>1</v>
       </c>
       <c r="L59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="1">
         <v>0</v>
@@ -5904,61 +5876,61 @@
         <v>0</v>
       </c>
       <c r="R59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U59" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="1">
-        <v>0</v>
-      </c>
-      <c r="W59" s="10">
-        <v>1</v>
-      </c>
-      <c r="X59" s="10">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="W59" s="1">
+        <v>1</v>
+      </c>
+      <c r="X59" s="1">
+        <v>0</v>
       </c>
       <c r="Y59" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA59" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB59" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA59" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="16">
+        <v>0</v>
       </c>
       <c r="AC59" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD59" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD59" s="1">
+        <v>0</v>
       </c>
       <c r="AE59" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A60" s="6"/>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A60" s="8"/>
       <c r="B60" s="1">
         <v>58</v>
       </c>
-      <c r="C60" s="12">
-        <v>0</v>
-      </c>
-      <c r="D60" s="9">
+      <c r="C60" s="7">
+        <v>0</v>
+      </c>
+      <c r="D60" s="5">
         <v>0</v>
       </c>
       <c r="E60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="1">
         <v>1</v>
@@ -5976,13 +5948,13 @@
         <v>1</v>
       </c>
       <c r="K60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" s="1">
         <v>0</v>
@@ -5994,61 +5966,61 @@
         <v>0</v>
       </c>
       <c r="Q60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V60" s="1">
         <v>1</v>
       </c>
-      <c r="W60" s="10">
-        <v>1</v>
-      </c>
-      <c r="X60" s="10">
-        <v>1</v>
+      <c r="W60" s="1">
+        <v>0</v>
+      </c>
+      <c r="X60" s="1">
+        <v>0</v>
       </c>
       <c r="Y60" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA60" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB60" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA60" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="16">
+        <v>0</v>
       </c>
       <c r="AC60" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD60" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1">
+        <v>0</v>
       </c>
       <c r="AE60" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A61" s="6"/>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A61" s="8"/>
       <c r="B61" s="1">
         <v>59</v>
       </c>
-      <c r="C61" s="12">
-        <v>0</v>
-      </c>
-      <c r="D61" s="9">
-        <v>0</v>
+      <c r="C61" s="7">
+        <v>0</v>
+      </c>
+      <c r="D61" s="5">
+        <v>1</v>
       </c>
       <c r="E61" s="1">
         <v>1</v>
@@ -6066,13 +6038,13 @@
         <v>1</v>
       </c>
       <c r="J61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" s="1">
         <v>0</v>
@@ -6084,63 +6056,63 @@
         <v>0</v>
       </c>
       <c r="P61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U61" s="1">
         <v>1</v>
       </c>
       <c r="V61" s="1">
-        <v>1</v>
-      </c>
-      <c r="W61" s="10">
-        <v>1</v>
-      </c>
-      <c r="X61" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W61" s="1">
+        <v>0</v>
+      </c>
+      <c r="X61" s="1">
+        <v>0</v>
       </c>
       <c r="Y61" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z61" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA61" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB61" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA61" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="16">
+        <v>0</v>
       </c>
       <c r="AC61" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD61" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD61" s="1">
+        <v>0</v>
       </c>
       <c r="AE61" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="A62" s="6"/>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A62" s="8"/>
       <c r="B62" s="1">
         <v>60</v>
       </c>
-      <c r="C62" s="12">
-        <v>0</v>
-      </c>
-      <c r="D62" s="9">
+      <c r="C62" s="7">
+        <v>1</v>
+      </c>
+      <c r="D62" s="5">
         <v>1</v>
       </c>
       <c r="E62" s="1">
@@ -6156,13 +6128,13 @@
         <v>1</v>
       </c>
       <c r="I62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -6174,52 +6146,52 @@
         <v>0</v>
       </c>
       <c r="O62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T62" s="1">
         <v>1</v>
       </c>
       <c r="U62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V62" s="1">
-        <v>1</v>
-      </c>
-      <c r="W62" s="10">
-        <v>1</v>
-      </c>
-      <c r="X62" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="W62" s="1">
+        <v>0</v>
+      </c>
+      <c r="X62" s="1">
+        <v>0</v>
       </c>
       <c r="Y62" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="12">
-        <v>1</v>
-      </c>
-      <c r="AB62" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AA62" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB62" s="16">
+        <v>0</v>
       </c>
       <c r="AC62" s="1">
-        <v>1</v>
-      </c>
-      <c r="AD62" s="10">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="AD62" s="1">
+        <v>0</v>
       </c>
       <c r="AE62" s="2">
         <v>1</v>
